--- a/443-sfe-lot-2-modification-du-role-du-participant-de-levenement/ig/ValueSet-tddui-encounter-type.xlsx
+++ b/443-sfe-lot-2-modification-du-role-du-participant-de-levenement/ig/ValueSet-tddui-encounter-type.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T15:47:52+00:00</t>
+    <t>2026-02-27T17:16:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
